--- a/data/Experiment/Raw/Spreadsheets/TheWorks_07242025.xlsx
+++ b/data/Experiment/Raw/Spreadsheets/TheWorks_07242025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/SeedlingMortality/data/Experiment/Raw/Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDF2C2F-8E12-2441-A347-6482A68A2E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FC93E4-37D4-D24E-8F83-19F1836B9A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9740" yWindow="760" windowWidth="19660" windowHeight="17060" activeTab="1" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
   </bookViews>
@@ -2206,7 +2206,7 @@
         <v>100</v>
       </c>
       <c r="B38">
-        <v>407.4</v>
+        <v>507.4</v>
       </c>
       <c r="C38" s="4">
         <v>0.1</v>
